--- a/artfynd/A 44664-2022 artfynd.xlsx
+++ b/artfynd/A 44664-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44664-2022 artfynd.xlsx
+++ b/artfynd/A 44664-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84572298</v>
+        <v>84572343</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579823.9984542832</v>
+        <v>579714</v>
       </c>
       <c r="R2" t="n">
-        <v>6572958.966383449</v>
+        <v>6572998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2020-04-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-04-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>7 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bergsluttning, mossig, barrskog</t>
+          <t>Granskog, mossig</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,59 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84572343</v>
+        <v>84571946</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rossvik, Nabben, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579713.63352997</v>
+        <v>580326</v>
       </c>
       <c r="R3" t="n">
-        <v>6572997.530145829</v>
+        <v>6572815</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,26 +859,11 @@
           <t>2020-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-04-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>7 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -919,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granskog, mossig</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,6 +890,335 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>84571947</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rossvik, Nabben, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>580096</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6572822</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-04-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-04-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bergsluttning, mossig, barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104655824</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nabben, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580002</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6572954</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>84572298</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rossvik, Nabben, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579824</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6572959</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-04-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-04-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bergsluttning, mossig, barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44664-2022 artfynd.xlsx
+++ b/artfynd/A 44664-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84571946</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84571947</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104655824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84572298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,8 +1244,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84572343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>